--- a/pacjenci/ADAM WOSIK.xlsx
+++ b/pacjenci/ADAM WOSIK.xlsx
@@ -483,7 +483,11 @@
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Inne</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>Do oceny</t>
@@ -523,10 +527,14 @@
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Inne</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brak aktywnej choroby</t>
+          <t>Do oceny</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -534,17 +542,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3 - wychwyt nie większy niż wątroba</t>
+          <t>4 - utrzymujący się wychwyt patologiczny</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Nie stwierdza się aktywnej metabolicznie choroby. Klasyfikacja Lugano: Complete Response (CR) - całkowita odpowiedź na leczenie. Deauville: 3 - wychwyt nie większy niż wątroba.</t>
+          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
         </is>
       </c>
     </row>
@@ -614,7 +622,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brak aktywnej choroby</t>
+          <t>Do oceny</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -622,17 +630,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3 - wychwyt nie większy niż wątroba</t>
+          <t>4 - utrzymujący się wychwyt patologiczny</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Nie stwierdza się aktywnej metabolicznie choroby. Klasyfikacja Lugano: Complete Response (CR) - całkowita odpowiedź na leczenie. Deauville: 3 - wychwyt nie większy niż wątroba.</t>
+          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
         </is>
       </c>
     </row>

--- a/pacjenci/ADAM WOSIK.xlsx
+++ b/pacjenci/ADAM WOSIK.xlsx
@@ -413,279 +413,209 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Nr badania</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Data badania</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nr badania</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Etap leczenia</t>
+          <t>Problem kliniczny</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Linia leczenia</t>
+          <t>Zakres badania</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Rozpoznanie</t>
+          <t>Opis badania</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Opis</t>
+          <t>Wnioski</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
           <t>SUVmax</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Ocena odpowiedzi</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Deauville</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Wnioski</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>05.01.2021</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>MCL. Ocena stopnia zaawansowania.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  57min od podania 18F-FDG. Glikemia: 148mg%.</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Pobudzone metabolicznie węzły chłonne: - w tkance podskórnej głowy [głównie w lewej okolicy potylicznej i podpotylicznej], wielkości do 12mm, SUV max do 3,4; - przedziału I- III obustronnie wielkości do 16mm, SUV max do 3,8. Miernie pobudzone metabolicznie węzły chłonne nadobojczykowe - głównie po stronie lewej - wielkości do 12mm, SUV max do 2,2. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Sklerotyzacja wyrostka sutkowatego piramidy prawej kości skroniowej. Nieco niejednorodne cieniowanie prawego płata tarczycy, z drobnymi zwapnieniami - do kontroli w USG.  Klatka piersiowa i śródpiersie: Aktywne i pobudzone metabolicznie węzły chłonne pachowe obustronnie wielkości do 33x19mm, SUV max do 4,2. Miernie pobudzone metabolicznie węzły chłonne w przyleganiu do struktur naczyniowych kończyny górnej prawej, SUV max do 1,7. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Nieaktywne metabolicznie węzły chłonne przytchawicze obustronnie wielkości do 12mm. Ok. 3mm obwodowy guzek w segm 3 płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Pobudzone metabolicznie węzły chłonne: - biodrowe wspólne lewe wielkości do 26mm, SUV max do 3,1; - biodrowe zewnętrzne obustronnie wielkości do 20mm, SUV max do 3,6; - pachwinowe obustronnie wielkości do 16mm, SUV max do 3,5. Odcinkowe pobudzenie metaboliczne w jelitach- czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Torbiele wątroby wielkości do 14x18mm.  Ok. 4mm uwapnione konkrementy w UKM-ach obu nerek.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Niewielka lewowypukła skolioza kręgosłupa lędźwiowego. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym kręgosłupa. Ciasne dyskopatie na poziomie L4/L5 i L5/S1. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w nałych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Drobne ubytki osteolityczne w masywach bocznych obu kości krzyżowych. Niejednorodnie, osteolitycznie przebudowany trzon kręgu Th2 oraz w mniejszym stopniu Th3 i L5. Drobne wyspy kostne w głowach obu kości ramiennych - więcej w prawej. Drobne wyspy kostne w głowach obu kości udowych.  Wartości referencyjne: MBPS SUVmax do 2,5; Prawy płat wątroby SUVmax do 3,4.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność głównie pobudzonych metabolicznie węzłów chłonnych po obu stronach przepony. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>4.2</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Nie dotyczy</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Aktywna metabolicznie choroba przed rozpoczęciem leczenia. Badanie wyjściowe stanowiące punkt odniesienia.</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>25.05.2021</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>MCL. Ocena chemiowrażliwości przed autoPBSCT.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  57 min od podania 18F-FDG. Glikemia: 117 mg%.</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Sklerotyzacja wyrostka sutkowatego piramidy prawej kości skroniowej. Nieco niejednorodne cieniowanie w przeglądowym badaniu TK prawego płata tarczycy, z drobnymi zwapnieniami - do kontroli w USG.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Węzły chłonne pachowe po stronie prawej wielkości do 14x7 mm; po stronie lewej wielkości do 14x8mm. Węzły chłonne przytchawicze obustronnie wielkości do 10 mm. W płatach górnych obu płuc - gorsze upowietrznienie oraz wydatne obszary o charakterze dyskretnej "mlecznej szyby". Podobne, mniej nasilone zmiany widoczne sa w płatach dolnych obu płuc. Ok. 3mm obwodowy guzek w segm 3 płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Rozlanie i odcinkowo wzmożony metabolizm FDG w jelitach SUV max do 8,0- w pierwszej kolejności związany ze stosowaniem biguanidu. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Węzły chłonne przy naczyniach biodrowych wspólnych lewych wielkości do 12 mm Torbiele wątroby wielkości do 15x18mm.  Ok. 4mm uwapnione konkrementy w UKM-ach obu nerek oraz pojedyncze ok. 3,5mm zwapnienie w miąższu nerki prawej.  Układ kostny: Niejednorodny metabolizm FDG w całym układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Niewielka lewowypukła skolioza kręgosłupa lędźwiowego. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym kręgosłupa. Ciasne dyskopatie na poziomie L4/L5 i L5/S1. Os sacrum arcuatum. Wielopoziomowo nierówne obrysy blaszek granicznych trzonów kręgowych. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Drobne ubytki osteolityczne w masywach bocznych obu kości krzyżowych. Niejednorodnie, osteolitycznie przebudowany trzon kręgu Th2 oraz w mniejszym stopniu Th3 i L5. Drobne wyspy kostne w głowach obu kości ramiennych - więcej w prawej. Drobne wyspy kostne w głowach obu kości udowych.  Wartości referencyjne: MBPS SUVmax do 2,1; Prawy płat wątroby SUVmax do 3,3.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono obecności aktywnej metabolicznie choroby chłoniakowej. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>8</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>17.08.2021</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Chłoniak z komórek płaszcza- dgn 12.2020. Aktualnie w trakcie III cyklu R-HAD. Ocena remisji choroby przed autoPBSCT.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  57 min od podania 18F-FDG. Glikemia: 97 mg%.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MCL</t>
+          <t>: Asymetryczne powiększenie migdałka podniebiennego lewego SUV max 3,0- do oceny w badaniu laryngologicznym. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Sklerotyzacja wyrostka sutkowatego piramidy prawej kości skroniowej. Nieco niejednorodne cieniowanie w przeglądowym badaniu TK prawego płata tarczycy, z drobnymi zwapnieniami - do kontroli w USG.  Klatka piersiowa i śródpiersie: Miernie pobudzone metabolicznie, drobne zmiany miąższowo-włókniste przykręgosłupowo w płacie dolnym płuca prawego SUV max do 2,6- w pierwszej kolejności zmiany zapalne - do kontroli po leczeniu Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Ok. 3mm obwodowy guzek w segm 3 płuca prawego. Ok. 1,5mm obwodowy guzek w segm. 3/4 płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Rozlanie i odcinkowo wzmożony metabolizm FDG w jelitach SUV max do 14,3 - w pierwszej kolejności związany ze stosowaniem biguanidu. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Węzły chłonne przyaortalnie po stronie lewej i przy naczyniach biodrowych wspólnych lewych wielkości do 11x10 mm. Torbiele wątroby wielkości do 15x18mm.  Ok. 4mm uwapnione konkrementy w UKM-ach obu nerek oraz pojedyncze ok. 3,5mm zwapnienie w miąższu nerki prawej. Prostata z drobnymi zwapnieniami.  Układ kostny: Niejednorodny metabolizm FDG w całym układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Niewielka lewowypukła skolioza kręgosłupa lędźwiowego. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym kręgosłupa. Ciasne dyskopatie na poziomie L4/L5 i L5/S1. Os sacrum arcuatum. Wielopoziomowo nierówne obrysy blaszek granicznych trzonów kręgowych. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Drobne ubytki osteolityczne w masywach bocznych obu kości krzyżowych. Niejednorodnie, osteolitycznie przebudowany trzon kręgu Th2 [i wyrostek poprzeczny lewy] oraz w mniejszym stopniu trzony Th3 i L5. Drobne wyspy kostne w głowach obu kości ramiennych - więcej w prawej. Drobne wyspy kostne w głowach obu kości udowych.  Wartości referencyjne: MBPS SUVmax do 2,1; Prawy płat wątroby SUVmax do 3,9.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono miernie pobudzone metabolicznie, drobne zmiany miąższowo-włókniste przykręgosłupowo w płacie dolnym płuca prawego- w pierwszej kolejności zmiany zapalne - do kontroli po leczeniu. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>14.3</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>20.01.2022</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>4</v>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>Chłoniak z komórek płaszcza- dgn 12.2020. Ocena remisji choroby po HDT+ autoPBSCT.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  57 min od podania 18F-FDG. Glikemia: 95 mg%.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MCL</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Sklerotyzacja wyrostka sutkowatego piramidy prawej kości skroniowej. Nieco niejednorodne cieniowanie w przeglądowym badaniu TK prawego płata tarczycy, z drobnymi zwapnieniami - do kontroli w USG.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Ok. 3mm obwodowy guzek w segm 3 płuca prawego. Ok. 1,5mm obwodowy guzek w segm. 3/4 płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Ślad płynu w jamach opłucnowych obustronnie.  Brzuch i miednica: Rozlanie i odcinkowo wzmożony metabolizm FDG w jelitach SUV max do 14,5 - w pierwszej kolejności związany ze stosowaniem biguanidu. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Węzły chłonne przyaortalnie po stronie lewej i przy naczyniach biodrowych wspólnych lewych wielkości do 11x9 mm. Torbiele wątroby wielkości do 15x18mm.  Ok. 4mm uwapnione konkrementy w UKM-ach obu nerek oraz pojedyncze ok. 3,5mm zwapnienie w miąższu nerki prawej. Prostata z drobnymi zwapnieniami.  Układ kostny: Fizjologiczny metabolizm FDG w całym układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Niewielka lewowypukła skolioza kręgosłupa lędźwiowego. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym kręgosłupa. Ciasne dyskopatie na poziomie L4/L5 i L5/S1. Os sacrum arcuatum. Wielopoziomowo nierówne obrysy blaszek granicznych trzonów kręgowych. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Drobne ubytki osteolityczne w masywach bocznych obu kości krzyżowych. Niejednorodnie, osteolitycznie przebudowany trzon kręgu Th2 [i wyrostek poprzeczny lewy] oraz w mniejszym stopniu trzony Th3 i L5. Drobne wyspy kostne w głowach obu kości ramiennych - więcej w prawej. Drobne wyspy kostne w głowach obu kości udowych.  Wartości referencyjne: MBPS SUVmax do 2,2; Prawy płat wątroby SUVmax do 3,1.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono obecności aktywnej metabolicznie choroby chłoniakowej. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>14.5</v>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>26.10.2022</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>5</v>
-      </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>Chłoniak z komórek płaszcza- dgn 12.2020. Ocena remisji choroby po HDT+ autoPBSCT.</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 61 min od podania 18F-FDG. Glikemia: 138 mg%.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MCL</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Sklerotyzacja wyrostka sutkowatego piramidy prawej kości skroniowej. Drobne zgrubienia błony śluzowej w zachyłku zębodołowym prawej zatoki szczękowej.  Nieco niejednorodne cieniowanie w przeglądowym badaniu TK prawego płata tarczycy, z drobnymi zwapnieniami - do kontroli w USG.  Klatka piersiowa i śródpiersie: Miernie pobudzona metabolicznie zmiana guzkowo-naciekowa w segmencie1+2 płuca lewego wielkości 19x14 mm, SUV max 3,1 [Im fuz. 101]. Miernie pobudzone metabolicznie zmiany miąższowe w grzbietowych częściach płatów dolnych obu płuc, zwłaszcza po stronie prawej, SUV max do 3,2- zmiany zapalne? Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Liczne rozsiane obszary o typie  mlecznego szkła oraz wyraźnych konsolidujących się zagęszczeń miąższowych w miąższu obu płuc- jak w infekcji wirusowej/COVID. Ok. 3mm obwodowy guzek w segm 3 płuca prawego. Ok. 7mm obwodowy guzek w segm. 3/4 płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Rozlanie i odcinkowo wzmożony metabolizm FDG w jelitach SUV max do 14,1 - w pierwszej kolejności związany ze stosowaniem biguanidu. Niejednorodny metabolizm FDG w wątrobie.Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Drobne węzły chłonne przyaortalnie po stronie lewej i przy naczyniach biodrowych wspólnych lewych. Torbiele wątroby wielkości do 15x18mm.  Ok. 4mm uwapnione konkrementy w UKM-ach obu nerek oraz pojedyncze ok. 3,5mm zwapnienie w miąższu nerki prawej. Prostata z drobnymi zwapnieniami.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Niewielka lewowypukła skolioza kręgosłupa lędźwiowego. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym kręgosłupa. Ciasne dyskopatie na poziomie L4/L5 i L5/S1. Os sacrum arcuatum. Wielopoziomowo nierówne obrysy blaszek granicznych trzonów kręgowych. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Drobne ubytki osteolityczne w masywach bocznych obu kości krzyżowych. Niejednorodnie, osteolitycznie przebudowany trzon kręgu Th2 [i wyrostek poprzeczny lewy] oraz w mniejszym stopniu trzony Th3 i L5. Drobne wyspy kostne w głowach obu kości ramiennych - więcej w prawej. Drobne wyspy kostne w głowach obu kości udowych.  Wartości referencyjne: MBPS SUVmax do 2,7; Prawy płat wątroby SUVmax do 5,1.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność: - miernie pobudzonej metabolicznie zmiany guzkowo-naciekowej w segmencie1+2 płuca lewego - do weryfikacji histopatologicznej. - miernie pobudzonych metabolicznie zmian miąższowych w miąższu obu płuc, zwłaszcza po stronie prawej- zmiany zapalne?- do kontroli. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>14.1</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/pacjenci/ADAM WOSIK.xlsx
+++ b/pacjenci/ADAM WOSIK.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Nr badania</t>
+          <t>Nr PET</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -439,17 +439,42 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Opis badania</t>
+          <t>Glikemia</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Czas po FDG</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Głowa i szyja</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Klatka piersiowa</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Brzuch i miednica</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Układ kostny</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>Wnioski</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>SUVmax</t>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>SUVmax_global</t>
         </is>
       </c>
     </row>
@@ -469,20 +494,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  57min od podania 18F-FDG. Glikemia: 148mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>: Pobudzone metabolicznie węzły chłonne: - w tkance podskórnej głowy [głównie w lewej okolicy potylicznej i podpotylicznej], wielkości do 12mm, SUV max do 3,4; - przedziału I- III obustronnie wielkości do 16mm, SUV max do 3,8. Miernie pobudzone metabolicznie węzły chłonne nadobojczykowe - głównie po stronie lewej - wielkości do 12mm, SUV max do 2,2. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Sklerotyzacja wyrostka sutkowatego piramidy prawej kości skroniowej. Nieco niejednorodne cieniowanie prawego płata tarczycy, z drobnymi zwapnieniami - do kontroli w USG.  Klatka piersiowa i śródpiersie: Aktywne i pobudzone metabolicznie węzły chłonne pachowe obustronnie wielkości do 33x19mm, SUV max do 4,2. Miernie pobudzone metabolicznie węzły chłonne w przyleganiu do struktur naczyniowych kończyny górnej prawej, SUV max do 1,7. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Nieaktywne metabolicznie węzły chłonne przytchawicze obustronnie wielkości do 12mm. Ok. 3mm obwodowy guzek w segm 3 płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Pobudzone metabolicznie węzły chłonne: - biodrowe wspólne lewe wielkości do 26mm, SUV max do 3,1; - biodrowe zewnętrzne obustronnie wielkości do 20mm, SUV max do 3,6; - pachwinowe obustronnie wielkości do 16mm, SUV max do 3,5. Odcinkowe pobudzenie metaboliczne w jelitach- czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Torbiele wątroby wielkości do 14x18mm.  Ok. 4mm uwapnione konkrementy w UKM-ach obu nerek.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Niewielka lewowypukła skolioza kręgosłupa lędźwiowego. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym kręgosłupa. Ciasne dyskopatie na poziomie L4/L5 i L5/S1. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w nałych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Drobne ubytki osteolityczne w masywach bocznych obu kości krzyżowych. Niejednorodnie, osteolitycznie przebudowany trzon kręgu Th2 oraz w mniejszym stopniu Th3 i L5. Drobne wyspy kostne w głowach obu kości ramiennych - więcej w prawej. Drobne wyspy kostne w głowach obu kości udowych.  Wartości referencyjne: MBPS SUVmax do 2,5; Prawy płat wątroby SUVmax do 3,4.</t>
+          <t>148</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Pobudzone metabolicznie węzły chłonne: - w tkance podskórnej głowy [głównie w lewej okolicy potylicznej i podpotylicznej], wielkości do 12mm, SUV max do 3,4; - przedziału I- III obustronnie wielkości do 16mm, SUV max do 3,8. Miernie pobudzone metabolicznie węzły chłonne nadobojczykowe - głównie po stronie lewej - wielkości do 12mm, SUV max do 2,2. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Sklerotyzacja wyrostka sutkowatego piramidy prawej kości skroniowej. Nieco niejednorodne cieniowanie prawego płata tarczycy, z drobnymi zwapnieniami - do kontroli w USG.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Aktywne i pobudzone metabolicznie węzły chłonne pachowe obustronnie wielkości do 33x19mm, SUV max do 4,2. Miernie pobudzone metabolicznie węzły chłonne w przyleganiu do struktur naczyniowych kończyny górnej prawej, SUV max do 1,7. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Nieaktywne metabolicznie węzły chłonne przytchawicze obustronnie wielkości do 12mm. Ok. 3mm obwodowy guzek w segm 3 płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Pobudzone metabolicznie węzły chłonne: - biodrowe wspólne lewe wielkości do 26mm, SUV max do 3,1; - biodrowe zewnętrzne obustronnie wielkości do 20mm, SUV max do 3,6; - pachwinowe obustronnie wielkości do 16mm, SUV max do 3,5. Odcinkowe pobudzenie metaboliczne w jelitach- czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Torbiele wątroby wielkości do 14x18mm.  Ok. 4mm uwapnione konkrementy w UKM-ach obu nerek.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Niewielka lewowypukła skolioza kręgosłupa lędźwiowego. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym kręgosłupa. Ciasne dyskopatie na poziomie L4/L5 i L5/S1. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w nałych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Drobne ubytki osteolityczne w masywach bocznych obu kości krzyżowych. Niejednorodnie, osteolitycznie przebudowany trzon kręgu Th2 oraz w mniejszym stopniu Th3 i L5. Drobne wyspy kostne w głowach obu kości ramiennych - więcej w prawej. Drobne wyspy kostne w głowach obu kości udowych.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność głównie pobudzonych metabolicznie węzłów chłonnych po obu stronach przepony. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="L2" t="n">
         <v>4.2</v>
       </c>
     </row>
@@ -502,20 +552,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  57 min od podania 18F-FDG. Glikemia: 117 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Sklerotyzacja wyrostka sutkowatego piramidy prawej kości skroniowej. Nieco niejednorodne cieniowanie w przeglądowym badaniu TK prawego płata tarczycy, z drobnymi zwapnieniami - do kontroli w USG.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Węzły chłonne pachowe po stronie prawej wielkości do 14x7 mm; po stronie lewej wielkości do 14x8mm. Węzły chłonne przytchawicze obustronnie wielkości do 10 mm. W płatach górnych obu płuc - gorsze upowietrznienie oraz wydatne obszary o charakterze dyskretnej "mlecznej szyby". Podobne, mniej nasilone zmiany widoczne sa w płatach dolnych obu płuc. Ok. 3mm obwodowy guzek w segm 3 płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Rozlanie i odcinkowo wzmożony metabolizm FDG w jelitach SUV max do 8,0- w pierwszej kolejności związany ze stosowaniem biguanidu. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Węzły chłonne przy naczyniach biodrowych wspólnych lewych wielkości do 12 mm Torbiele wątroby wielkości do 15x18mm.  Ok. 4mm uwapnione konkrementy w UKM-ach obu nerek oraz pojedyncze ok. 3,5mm zwapnienie w miąższu nerki prawej.  Układ kostny: Niejednorodny metabolizm FDG w całym układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Niewielka lewowypukła skolioza kręgosłupa lędźwiowego. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym kręgosłupa. Ciasne dyskopatie na poziomie L4/L5 i L5/S1. Os sacrum arcuatum. Wielopoziomowo nierówne obrysy blaszek granicznych trzonów kręgowych. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Drobne ubytki osteolityczne w masywach bocznych obu kości krzyżowych. Niejednorodnie, osteolitycznie przebudowany trzon kręgu Th2 oraz w mniejszym stopniu Th3 i L5. Drobne wyspy kostne w głowach obu kości ramiennych - więcej w prawej. Drobne wyspy kostne w głowach obu kości udowych.  Wartości referencyjne: MBPS SUVmax do 2,1; Prawy płat wątroby SUVmax do 3,3.</t>
+          <t>117</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Sklerotyzacja wyrostka sutkowatego piramidy prawej kości skroniowej. Nieco niejednorodne cieniowanie w przeglądowym badaniu TK prawego płata tarczycy, z drobnymi zwapnieniami - do kontroli w USG.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Węzły chłonne pachowe po stronie prawej wielkości do 14x7 mm; po stronie lewej wielkości do 14x8mm. Węzły chłonne przytchawicze obustronnie wielkości do 10 mm. W płatach górnych obu płuc - gorsze upowietrznienie oraz wydatne obszary o charakterze dyskretnej "mlecznej szyby". Podobne, mniej nasilone zmiany widoczne sa w płatach dolnych obu płuc. Ok. 3mm obwodowy guzek w segm 3 płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Rozlanie i odcinkowo wzmożony metabolizm FDG w jelitach SUV max do 8,0- w pierwszej kolejności związany ze stosowaniem biguanidu. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Węzły chłonne przy naczyniach biodrowych wspólnych lewych wielkości do 12 mm Torbiele wątroby wielkości do 15x18mm.  Ok. 4mm uwapnione konkrementy w UKM-ach obu nerek oraz pojedyncze ok. 3,5mm zwapnienie w miąższu nerki prawej.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Niejednorodny metabolizm FDG w całym układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Niewielka lewowypukła skolioza kręgosłupa lędźwiowego. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym kręgosłupa. Ciasne dyskopatie na poziomie L4/L5 i L5/S1. Os sacrum arcuatum. Wielopoziomowo nierówne obrysy blaszek granicznych trzonów kręgowych. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Drobne ubytki osteolityczne w masywach bocznych obu kości krzyżowych. Niejednorodnie, osteolitycznie przebudowany trzon kręgu Th2 oraz w mniejszym stopniu Th3 i L5. Drobne wyspy kostne w głowach obu kości ramiennych - więcej w prawej. Drobne wyspy kostne w głowach obu kości udowych.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono obecności aktywnej metabolicznie choroby chłoniakowej. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="L3" t="n">
         <v>8</v>
       </c>
     </row>
@@ -535,20 +610,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  57 min od podania 18F-FDG. Glikemia: 97 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>: Asymetryczne powiększenie migdałka podniebiennego lewego SUV max 3,0- do oceny w badaniu laryngologicznym. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Sklerotyzacja wyrostka sutkowatego piramidy prawej kości skroniowej. Nieco niejednorodne cieniowanie w przeglądowym badaniu TK prawego płata tarczycy, z drobnymi zwapnieniami - do kontroli w USG.  Klatka piersiowa i śródpiersie: Miernie pobudzone metabolicznie, drobne zmiany miąższowo-włókniste przykręgosłupowo w płacie dolnym płuca prawego SUV max do 2,6- w pierwszej kolejności zmiany zapalne - do kontroli po leczeniu Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Ok. 3mm obwodowy guzek w segm 3 płuca prawego. Ok. 1,5mm obwodowy guzek w segm. 3/4 płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Rozlanie i odcinkowo wzmożony metabolizm FDG w jelitach SUV max do 14,3 - w pierwszej kolejności związany ze stosowaniem biguanidu. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Węzły chłonne przyaortalnie po stronie lewej i przy naczyniach biodrowych wspólnych lewych wielkości do 11x10 mm. Torbiele wątroby wielkości do 15x18mm.  Ok. 4mm uwapnione konkrementy w UKM-ach obu nerek oraz pojedyncze ok. 3,5mm zwapnienie w miąższu nerki prawej. Prostata z drobnymi zwapnieniami.  Układ kostny: Niejednorodny metabolizm FDG w całym układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Niewielka lewowypukła skolioza kręgosłupa lędźwiowego. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym kręgosłupa. Ciasne dyskopatie na poziomie L4/L5 i L5/S1. Os sacrum arcuatum. Wielopoziomowo nierówne obrysy blaszek granicznych trzonów kręgowych. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Drobne ubytki osteolityczne w masywach bocznych obu kości krzyżowych. Niejednorodnie, osteolitycznie przebudowany trzon kręgu Th2 [i wyrostek poprzeczny lewy] oraz w mniejszym stopniu trzony Th3 i L5. Drobne wyspy kostne w głowach obu kości ramiennych - więcej w prawej. Drobne wyspy kostne w głowach obu kości udowych.  Wartości referencyjne: MBPS SUVmax do 2,1; Prawy płat wątroby SUVmax do 3,9.</t>
+          <t>97</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Asymetryczne powiększenie migdałka podniebiennego lewego SUV max 3,0- do oceny w badaniu laryngologicznym. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Sklerotyzacja wyrostka sutkowatego piramidy prawej kości skroniowej. Nieco niejednorodne cieniowanie w przeglądowym badaniu TK prawego płata tarczycy, z drobnymi zwapnieniami - do kontroli w USG.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Miernie pobudzone metabolicznie, drobne zmiany miąższowo-włókniste przykręgosłupowo w płacie dolnym płuca prawego SUV max do 2,6- w pierwszej kolejności zmiany zapalne - do kontroli po leczeniu Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Ok. 3mm obwodowy guzek w segm 3 płuca prawego. Ok. 1,5mm obwodowy guzek w segm. 3/4 płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Rozlanie i odcinkowo wzmożony metabolizm FDG w jelitach SUV max do 14,3 - w pierwszej kolejności związany ze stosowaniem biguanidu. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Węzły chłonne przyaortalnie po stronie lewej i przy naczyniach biodrowych wspólnych lewych wielkości do 11x10 mm. Torbiele wątroby wielkości do 15x18mm.  Ok. 4mm uwapnione konkrementy w UKM-ach obu nerek oraz pojedyncze ok. 3,5mm zwapnienie w miąższu nerki prawej. Prostata z drobnymi zwapnieniami.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Niejednorodny metabolizm FDG w całym układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Niewielka lewowypukła skolioza kręgosłupa lędźwiowego. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym kręgosłupa. Ciasne dyskopatie na poziomie L4/L5 i L5/S1. Os sacrum arcuatum. Wielopoziomowo nierówne obrysy blaszek granicznych trzonów kręgowych. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Drobne ubytki osteolityczne w masywach bocznych obu kości krzyżowych. Niejednorodnie, osteolitycznie przebudowany trzon kręgu Th2 [i wyrostek poprzeczny lewy] oraz w mniejszym stopniu trzony Th3 i L5. Drobne wyspy kostne w głowach obu kości ramiennych - więcej w prawej. Drobne wyspy kostne w głowach obu kości udowych.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono miernie pobudzone metabolicznie, drobne zmiany miąższowo-włókniste przykręgosłupowo w płacie dolnym płuca prawego- w pierwszej kolejności zmiany zapalne - do kontroli po leczeniu. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="L4" t="n">
         <v>14.3</v>
       </c>
     </row>
@@ -568,20 +668,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  57 min od podania 18F-FDG. Glikemia: 95 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Sklerotyzacja wyrostka sutkowatego piramidy prawej kości skroniowej. Nieco niejednorodne cieniowanie w przeglądowym badaniu TK prawego płata tarczycy, z drobnymi zwapnieniami - do kontroli w USG.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Ok. 3mm obwodowy guzek w segm 3 płuca prawego. Ok. 1,5mm obwodowy guzek w segm. 3/4 płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Ślad płynu w jamach opłucnowych obustronnie.  Brzuch i miednica: Rozlanie i odcinkowo wzmożony metabolizm FDG w jelitach SUV max do 14,5 - w pierwszej kolejności związany ze stosowaniem biguanidu. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Węzły chłonne przyaortalnie po stronie lewej i przy naczyniach biodrowych wspólnych lewych wielkości do 11x9 mm. Torbiele wątroby wielkości do 15x18mm.  Ok. 4mm uwapnione konkrementy w UKM-ach obu nerek oraz pojedyncze ok. 3,5mm zwapnienie w miąższu nerki prawej. Prostata z drobnymi zwapnieniami.  Układ kostny: Fizjologiczny metabolizm FDG w całym układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Niewielka lewowypukła skolioza kręgosłupa lędźwiowego. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym kręgosłupa. Ciasne dyskopatie na poziomie L4/L5 i L5/S1. Os sacrum arcuatum. Wielopoziomowo nierówne obrysy blaszek granicznych trzonów kręgowych. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Drobne ubytki osteolityczne w masywach bocznych obu kości krzyżowych. Niejednorodnie, osteolitycznie przebudowany trzon kręgu Th2 [i wyrostek poprzeczny lewy] oraz w mniejszym stopniu trzony Th3 i L5. Drobne wyspy kostne w głowach obu kości ramiennych - więcej w prawej. Drobne wyspy kostne w głowach obu kości udowych.  Wartości referencyjne: MBPS SUVmax do 2,2; Prawy płat wątroby SUVmax do 3,1.</t>
+          <t>95</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Sklerotyzacja wyrostka sutkowatego piramidy prawej kości skroniowej. Nieco niejednorodne cieniowanie w przeglądowym badaniu TK prawego płata tarczycy, z drobnymi zwapnieniami - do kontroli w USG.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Ok. 3mm obwodowy guzek w segm 3 płuca prawego. Ok. 1,5mm obwodowy guzek w segm. 3/4 płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Ślad płynu w jamach opłucnowych obustronnie.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Rozlanie i odcinkowo wzmożony metabolizm FDG w jelitach SUV max do 14,5 - w pierwszej kolejności związany ze stosowaniem biguanidu. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Węzły chłonne przyaortalnie po stronie lewej i przy naczyniach biodrowych wspólnych lewych wielkości do 11x9 mm. Torbiele wątroby wielkości do 15x18mm.  Ok. 4mm uwapnione konkrementy w UKM-ach obu nerek oraz pojedyncze ok. 3,5mm zwapnienie w miąższu nerki prawej. Prostata z drobnymi zwapnieniami.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w całym układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Niewielka lewowypukła skolioza kręgosłupa lędźwiowego. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym kręgosłupa. Ciasne dyskopatie na poziomie L4/L5 i L5/S1. Os sacrum arcuatum. Wielopoziomowo nierówne obrysy blaszek granicznych trzonów kręgowych. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Drobne ubytki osteolityczne w masywach bocznych obu kości krzyżowych. Niejednorodnie, osteolitycznie przebudowany trzon kręgu Th2 [i wyrostek poprzeczny lewy] oraz w mniejszym stopniu trzony Th3 i L5. Drobne wyspy kostne w głowach obu kości ramiennych - więcej w prawej. Drobne wyspy kostne w głowach obu kości udowych.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono obecności aktywnej metabolicznie choroby chłoniakowej. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="L5" t="n">
         <v>14.5</v>
       </c>
     </row>
@@ -601,20 +726,45 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 61 min od podania 18F-FDG. Glikemia: 138 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Sklerotyzacja wyrostka sutkowatego piramidy prawej kości skroniowej. Drobne zgrubienia błony śluzowej w zachyłku zębodołowym prawej zatoki szczękowej.  Nieco niejednorodne cieniowanie w przeglądowym badaniu TK prawego płata tarczycy, z drobnymi zwapnieniami - do kontroli w USG.  Klatka piersiowa i śródpiersie: Miernie pobudzona metabolicznie zmiana guzkowo-naciekowa w segmencie1+2 płuca lewego wielkości 19x14 mm, SUV max 3,1 [Im fuz. 101]. Miernie pobudzone metabolicznie zmiany miąższowe w grzbietowych częściach płatów dolnych obu płuc, zwłaszcza po stronie prawej, SUV max do 3,2- zmiany zapalne? Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Liczne rozsiane obszary o typie  mlecznego szkła oraz wyraźnych konsolidujących się zagęszczeń miąższowych w miąższu obu płuc- jak w infekcji wirusowej/COVID. Ok. 3mm obwodowy guzek w segm 3 płuca prawego. Ok. 7mm obwodowy guzek w segm. 3/4 płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Rozlanie i odcinkowo wzmożony metabolizm FDG w jelitach SUV max do 14,1 - w pierwszej kolejności związany ze stosowaniem biguanidu. Niejednorodny metabolizm FDG w wątrobie.Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Drobne węzły chłonne przyaortalnie po stronie lewej i przy naczyniach biodrowych wspólnych lewych. Torbiele wątroby wielkości do 15x18mm.  Ok. 4mm uwapnione konkrementy w UKM-ach obu nerek oraz pojedyncze ok. 3,5mm zwapnienie w miąższu nerki prawej. Prostata z drobnymi zwapnieniami.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Niewielka lewowypukła skolioza kręgosłupa lędźwiowego. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym kręgosłupa. Ciasne dyskopatie na poziomie L4/L5 i L5/S1. Os sacrum arcuatum. Wielopoziomowo nierówne obrysy blaszek granicznych trzonów kręgowych. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Drobne ubytki osteolityczne w masywach bocznych obu kości krzyżowych. Niejednorodnie, osteolitycznie przebudowany trzon kręgu Th2 [i wyrostek poprzeczny lewy] oraz w mniejszym stopniu trzony Th3 i L5. Drobne wyspy kostne w głowach obu kości ramiennych - więcej w prawej. Drobne wyspy kostne w głowach obu kości udowych.  Wartości referencyjne: MBPS SUVmax do 2,7; Prawy płat wątroby SUVmax do 5,1.</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Sklerotyzacja wyrostka sutkowatego piramidy prawej kości skroniowej. Drobne zgrubienia błony śluzowej w zachyłku zębodołowym prawej zatoki szczękowej.  Nieco niejednorodne cieniowanie w przeglądowym badaniu TK prawego płata tarczycy, z drobnymi zwapnieniami - do kontroli w USG.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Miernie pobudzona metabolicznie zmiana guzkowo-naciekowa w segmencie1+2 płuca lewego wielkości 19x14 mm, SUV max 3,1 [Im fuz. 101]. Miernie pobudzone metabolicznie zmiany miąższowe w grzbietowych częściach płatów dolnych obu płuc, zwłaszcza po stronie prawej, SUV max do 3,2- zmiany zapalne? Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Liczne rozsiane obszary o typie  mlecznego szkła oraz wyraźnych konsolidujących się zagęszczeń miąższowych w miąższu obu płuc- jak w infekcji wirusowej/COVID. Ok. 3mm obwodowy guzek w segm 3 płuca prawego. Ok. 7mm obwodowy guzek w segm. 3/4 płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Rozlanie i odcinkowo wzmożony metabolizm FDG w jelitach SUV max do 14,1 - w pierwszej kolejności związany ze stosowaniem biguanidu. Niejednorodny metabolizm FDG w wątrobie.Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Drobne węzły chłonne przyaortalnie po stronie lewej i przy naczyniach biodrowych wspólnych lewych. Torbiele wątroby wielkości do 15x18mm.  Ok. 4mm uwapnione konkrementy w UKM-ach obu nerek oraz pojedyncze ok. 3,5mm zwapnienie w miąższu nerki prawej. Prostata z drobnymi zwapnieniami.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Niewielka lewowypukła skolioza kręgosłupa lędźwiowego. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym kręgosłupa. Ciasne dyskopatie na poziomie L4/L5 i L5/S1. Os sacrum arcuatum. Wielopoziomowo nierówne obrysy blaszek granicznych trzonów kręgowych. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Drobne ubytki osteolityczne w masywach bocznych obu kości krzyżowych. Niejednorodnie, osteolitycznie przebudowany trzon kręgu Th2 [i wyrostek poprzeczny lewy] oraz w mniejszym stopniu trzony Th3 i L5. Drobne wyspy kostne w głowach obu kości ramiennych - więcej w prawej. Drobne wyspy kostne w głowach obu kości udowych.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność: - miernie pobudzonej metabolicznie zmiany guzkowo-naciekowej w segmencie1+2 płuca lewego - do weryfikacji histopatologicznej. - miernie pobudzonych metabolicznie zmian miąższowych w miąższu obu płuc, zwłaszcza po stronie prawej- zmiany zapalne?- do kontroli. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="L6" t="n">
         <v>14.1</v>
       </c>
     </row>
